--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122262051</v>
       </c>
       <c r="B2" t="n">
-        <v>94947</v>
+        <v>94957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122262051</v>
       </c>
       <c r="B2" t="n">
-        <v>94957</v>
+        <v>94969</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>122262074</v>
       </c>
       <c r="B3" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122262051</v>
+        <v>122262074</v>
       </c>
       <c r="B2" t="n">
-        <v>94969</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 58727, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>569025</v>
       </c>
       <c r="R2" t="n">
-        <v>6435042</v>
+        <v>6435015</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122262074</v>
+        <v>122262051</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>94974</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,53 +801,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 58727, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>569025</v>
       </c>
       <c r="R3" t="n">
-        <v>6435015</v>
+        <v>6435042</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122262074</v>
+        <v>122262051</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>94983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>2180</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58727, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>569025</v>
       </c>
       <c r="R2" t="n">
-        <v>6435015</v>
+        <v>6435042</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122262051</v>
+        <v>122262074</v>
       </c>
       <c r="B3" t="n">
-        <v>94974</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,45 +789,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 58727, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>569025</v>
       </c>
       <c r="R3" t="n">
-        <v>6435042</v>
+        <v>6435015</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +868,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122262051</v>
+        <v>122262074</v>
       </c>
       <c r="B2" t="n">
-        <v>94983</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103021</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 58727, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>569025</v>
       </c>
       <c r="R2" t="n">
-        <v>6435042</v>
+        <v>6435015</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122262074</v>
+        <v>122262051</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>94996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,48 +801,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 58727, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>569025</v>
       </c>
       <c r="R3" t="n">
-        <v>6435015</v>
+        <v>6435042</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>122262051</v>
       </c>
       <c r="B3" t="n">
-        <v>94996</v>
+        <v>95009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122262074</v>
+        <v>122262051</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>95011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58727, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>569025</v>
       </c>
       <c r="R2" t="n">
-        <v>6435015</v>
+        <v>6435042</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122262051</v>
+        <v>122262074</v>
       </c>
       <c r="B3" t="n">
-        <v>95009</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,45 +794,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 58727, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>569025</v>
       </c>
       <c r="R3" t="n">
-        <v>6435042</v>
+        <v>6435015</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122262051</v>
+        <v>122262074</v>
       </c>
       <c r="B2" t="n">
-        <v>95011</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>A 58727, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>569025</v>
       </c>
       <c r="R2" t="n">
-        <v>6435042</v>
+        <v>6435015</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122262074</v>
+        <v>122262051</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>95011</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,53 +801,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 58727, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>569025</v>
       </c>
       <c r="R3" t="n">
-        <v>6435015</v>
+        <v>6435042</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122262074</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>122262051</v>
       </c>
       <c r="B3" t="n">
-        <v>95011</v>
+        <v>95012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,6 +894,130 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122909814</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57394</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Pjäkebo Tallberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>569047</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6434958</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>122909814</v>
       </c>
       <c r="B4" t="n">
-        <v>57394</v>
+        <v>57397</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>122909814</v>
       </c>
       <c r="B4" t="n">
-        <v>57397</v>
+        <v>57403</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,122 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128131765</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57830</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pjäkebo Tallberget, Pjäkebo Tallberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>569021</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6435033</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -1144,7 +1144,7 @@
         <v>128131765</v>
       </c>
       <c r="B6" t="n">
-        <v>57830</v>
+        <v>57831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -1144,7 +1144,7 @@
         <v>128131765</v>
       </c>
       <c r="B6" t="n">
-        <v>57831</v>
+        <v>57843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -1144,7 +1144,7 @@
         <v>128131765</v>
       </c>
       <c r="B6" t="n">
-        <v>57843</v>
+        <v>57847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58727-2024 artfynd.xlsx
+++ b/artfynd/A 58727-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122262074</v>
+        <v>122262051</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58727, Pjäkebo, Sm</t>
+          <t>A 58427, Pjäkebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>569025</v>
       </c>
       <c r="R2" t="n">
-        <v>6435015</v>
+        <v>6435042</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122262051</v>
+        <v>124264901</v>
       </c>
       <c r="B3" t="n">
-        <v>95012</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,41 +788,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 58427, Pjäkebo, Sm</t>
+          <t>Pjäkebo Tallberget, Pjäkebo Tallberget, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569025</v>
+        <v>569009</v>
       </c>
       <c r="R3" t="n">
-        <v>6435042</v>
+        <v>6434999</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,12 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-04-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,19 +875,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Björn Stenberg</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -899,16 +896,11 @@
         <v>122909814</v>
       </c>
       <c r="B4" t="n">
-        <v>57403</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1020,15 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124264901</v>
+        <v>128131837</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,16 +1023,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100090</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1069,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569009</v>
+        <v>569018</v>
       </c>
       <c r="R5" t="n">
-        <v>6434999</v>
+        <v>6435070</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,22 +1086,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,7 +1131,7 @@
         <v>128131765</v>
       </c>
       <c r="B6" t="n">
-        <v>57847</v>
+        <v>58112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,6 +1241,115 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122262074</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 58727, Pjäkebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>569025</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6435015</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
